--- a/tests/data/parser/transmission/results_transmission_mix_rate_expected.xlsx
+++ b/tests/data/parser/transmission/results_transmission_mix_rate_expected.xlsx
@@ -375,7 +375,7 @@
         </is>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="198" customHeight="1">
+    <row r="4" s="1" customFormat="1" ht="252" customHeight="1">
       <c r="A4" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Transceiver trx Lannion_CAS
@@ -388,6 +388,9 @@
 	- PDL:: mode_1: 0.00, mode_2: 0.00 dB
 	- Latency: 0.0 ms
 	- Actual pch out:: mode_1: 0.00, mode_2: 0.00 dBm
+	- CD penalty: None dB
+	- PMD penalty:: None dB
+	- PDL penalty:: None dB
 </t>
         </is>
       </c>
@@ -503,6 +506,9 @@
 	- PDL:: mode_1: 0.00, mode_2: 0.00 dB
 	- Latency: 0.64 ms
 	- Actual pch out:: mode_1: 0.00, mode_2: 0.00 dBm
+	- CD penalty: None dB
+	- PMD penalty:: None dB
+	- PDL penalty:: None dB
 </t>
         </is>
       </c>

--- a/tests/data/parser/transmission/results_transmission_mix_rate_expected.xlsx
+++ b/tests/data/parser/transmission/results_transmission_mix_rate_expected.xlsx
@@ -388,9 +388,6 @@
 	- PDL:: mode_1: 0.00, mode_2: 0.00 dB
 	- Latency: 0.0 ms
 	- Actual pch out:: mode_1: 0.00, mode_2: 0.00 dBm
-	- CD penalty: None dB
-	- PMD penalty:: None dB
-	- PDL penalty:: None dB
 </t>
         </is>
       </c>
